--- a/assets/targetSeqFeaturesTable.xlsx
+++ b/assets/targetSeqFeaturesTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Dropbox (UMass Medical School)/LabProjects/shortInsertKnockin/Annotations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaihu/Projects/Analytical_projects/Nathan/sikipipe/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DA509B-B5E8-EA48-A9FF-2958CEA87708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D00986-E709-CC42-B601-48D3E98D212F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="1060" windowWidth="18680" windowHeight="16740" xr2:uid="{D609BC35-E87A-E54B-B3FA-361EE73E021E}"/>
+    <workbookView minimized="1" xWindow="3620" yWindow="1700" windowWidth="23560" windowHeight="16300" xr2:uid="{D609BC35-E87A-E54B-B3FA-361EE73E021E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -189,12 +189,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -209,9 +221,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -232,7 +250,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -520,7 +538,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -638,25 +656,25 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2">
         <v>1275</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="2">
         <v>1294</v>
       </c>
     </row>
@@ -707,25 +725,25 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="3">
         <v>1279</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="3">
         <v>1368</v>
       </c>
     </row>
@@ -776,25 +794,25 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="1">
+      <c r="E13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2">
         <v>863</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="2">
         <v>882</v>
       </c>
     </row>
@@ -822,25 +840,25 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="E15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="3">
         <v>860</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="3">
         <v>949</v>
       </c>
     </row>
@@ -867,7 +885,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -890,30 +908,30 @@
         <v>970</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="E18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2">
         <v>947</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="2">
         <v>966</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -936,7 +954,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -959,30 +977,30 @@
         <v>964</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="E21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3">
         <v>950</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="3">
         <v>1039</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1005,7 +1023,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1028,7 +1046,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
@@ -1051,7 +1069,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
@@ -1074,7 +1092,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1097,30 +1115,30 @@
         <v>998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="1">
+      <c r="E27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="3">
         <v>1000</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="3">
         <v>1089</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -1143,7 +1161,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
@@ -1166,7 +1184,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
@@ -1189,7 +1207,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>41</v>
       </c>
@@ -1212,28 +1230,29 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="E32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2">
         <v>1072</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="2">
         <v>1090</v>
       </c>
+      <c r="H32" s="2"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -1259,25 +1278,25 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="1">
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="3">
         <v>1085</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="3">
         <v>1177</v>
       </c>
     </row>

--- a/assets/targetSeqFeaturesTable.xlsx
+++ b/assets/targetSeqFeaturesTable.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10107"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaihu/Projects/Analytical_projects/Nathan/sikipipe/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D00986-E709-CC42-B601-48D3E98D212F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743866A9-E744-834B-9CBA-57CCB40E8F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3620" yWindow="1700" windowWidth="23560" windowHeight="16300" xr2:uid="{D609BC35-E87A-E54B-B3FA-361EE73E021E}"/>
+    <workbookView xWindow="1740" yWindow="2400" windowWidth="23560" windowHeight="16300" xr2:uid="{D609BC35-E87A-E54B-B3FA-361EE73E021E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="46">
   <si>
     <t>gene</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>crRNA</t>
+  </si>
+  <si>
+    <t>* Kai note: 1-based, inclusive coordinates at both sides</t>
+  </si>
+  <si>
+    <t>* Kai note: to convert to bed, minus 1 from the start coordinate</t>
   </si>
 </sst>
 </file>
@@ -250,7 +256,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -538,7 +544,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -546,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA068AD-BB1D-6E44-BBD1-647F56AA6564}">
-  <dimension ref="A3:H34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -560,6 +566,16 @@
     <col min="10" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
